--- a/live/data.xlsx
+++ b/live/data.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\郁敏\web\live\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\yumin\web\live\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="25600" windowHeight="12080" activeTab="1"/>
+    <workbookView windowWidth="25600" windowHeight="12080"/>
   </bookViews>
   <sheets>
     <sheet name="lives" sheetId="1" r:id="rId1"/>
@@ -63,10 +63,10 @@
     <t>中野サンプラザホール</t>
   </si>
   <si>
-    <t>../images/0th.png</t>
-  </si>
-  <si>
-    <t>../images/0th kv假.png</t>
+    <t>../images/0th.webp</t>
+  </si>
+  <si>
+    <t>../images/0th kv假.webp</t>
   </si>
   <si>
     <t>https://www.bilibili.com/video/BV1QsnXzBEWb/</t>
@@ -225,7 +225,7 @@
     <t>group_id</t>
   </si>
   <si>
-    <t>../images/0thlive返图1.jpg</t>
+    <t>../images/0thlive返图1.webp</t>
   </si>
   <si>
     <t>@bang_dream_info</t>
@@ -243,28 +243,28 @@
     <t>0th LIVE 官推</t>
   </si>
   <si>
-    <t>../images/0thlive返图2.jpg</t>
-  </si>
-  <si>
-    <t>../images/0thlive返图3.jpg</t>
-  </si>
-  <si>
-    <t>../images/0thlive返图4.jpg</t>
-  </si>
-  <si>
-    <t>../images/0thlive返图5.jpg</t>
-  </si>
-  <si>
-    <t>../images/0thlive返图6.jpg</t>
-  </si>
-  <si>
-    <t>../images/0thlive返图7.jpg</t>
-  </si>
-  <si>
-    <t>../images/0thlive返图8.jpg</t>
-  </si>
-  <si>
-    <t>../images/0thlive返图9.jpg</t>
+    <t>../images/0thlive返图2.webp</t>
+  </si>
+  <si>
+    <t>../images/0thlive返图3.webp</t>
+  </si>
+  <si>
+    <t>../images/0thlive返图4.webp</t>
+  </si>
+  <si>
+    <t>../images/0thlive返图5.webp</t>
+  </si>
+  <si>
+    <t>../images/0thlive返图6.webp</t>
+  </si>
+  <si>
+    <t>../images/0thlive返图7.webp</t>
+  </si>
+  <si>
+    <t>../images/0thlive返图8.webp</t>
+  </si>
+  <si>
+    <t>../images/0thlive返图9.webp</t>
   </si>
 </sst>
 </file>
